--- a/output/pdf_financials_xlsx/AUGC.xlsx
+++ b/output/pdf_financials_xlsx/AUGC.xlsx
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.020144</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.286828</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1017,7 +1017,7 @@
         <v>0.014</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.175776</v>
       </c>
     </row>
     <row r="18">
@@ -1142,22 +1142,22 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.010072</v>
+        <v>-0.010072</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.643414</v>
+        <v>-0.643414</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.151059</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.18597</v>
+        <v>-0.18597</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.112767</v>
+        <v>-0.112767</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.08788799999999999</v>
+        <v>-0.08788799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1248,22 +1248,22 @@
         <v>-0.044228</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.010072</v>
+        <v>-0.010072</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.643414</v>
+        <v>-0.643414</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.151059</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.18597</v>
+        <v>-0.18597</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.112767</v>
+        <v>-0.112767</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.08788799999999999</v>
+        <v>-0.08788799999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>16.08535</v>
+        <v>-16.08535</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -1589,7 +1589,7 @@
         <v>11.04388366057412</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -3812,19 +3812,19 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.067106</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.074256</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.074256</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.074256</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.074256</v>
       </c>
     </row>
     <row r="93">
@@ -6059,7 +6059,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -6358,7 +6362,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -6783,7 +6791,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -13290,13 +13302,13 @@
         <v>-0.151059</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>0.18597</v>
+        <v>-0.18597</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>0.112767</v>
+        <v>-0.112767</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>0.08788799999999999</v>
+        <v>-0.08788799999999999</v>
       </c>
     </row>
     <row r="132">
@@ -14321,10 +14333,10 @@
         </is>
       </c>
       <c r="I148" s="5" t="n">
-        <v>0.643414</v>
+        <v>-0.643414</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>0.151059</v>
+        <v>-0.151059</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -14995,10 +15007,10 @@
         </is>
       </c>
       <c r="H159" s="5" t="n">
-        <v>0.010072</v>
+        <v>-0.010072</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>0.643414</v>
+        <v>-0.643414</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AUGC.xlsx
+++ b/output/pdf_financials_xlsx/AUGC.xlsx
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.017377</v>
+        <v>0.124255</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.017377</v>
+        <v>-0.124255</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -825,19 +825,19 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007638</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009672999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006416</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00251</v>
       </c>
     </row>
     <row r="13">
@@ -1417,19 +1417,19 @@
         <v>0.010072</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.643414</v>
+        <v>0.643413</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.151059</v>
+        <v>-0.158697</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.17197</v>
+        <v>0.181643</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.126767</v>
+        <v>0.133183</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.08788799999999999</v>
+        <v>0.09039800000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1489,19 +1489,19 @@
         <v>0.010072</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.643414</v>
+        <v>0.643413</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.151059</v>
+        <v>-0.158697</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.17197</v>
+        <v>0.181643</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.126767</v>
+        <v>0.133183</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.08788799999999999</v>
+        <v>0.09039800000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1663,28 +1663,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.271758</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.219997</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.030178</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.731878</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.20913</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.213853</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.101561</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.031944</v>
       </c>
     </row>
     <row r="35">
@@ -1735,28 +1735,28 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.271758</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.219997</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.030178</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.731878</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.20913</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.213853</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.101561</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.031944</v>
       </c>
     </row>
     <row r="37">
@@ -2167,28 +2167,28 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.271758</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.219997</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.030178</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.745496</v>
+        <v>0.013618</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.27806</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.213853</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.107754</v>
+        <v>0.006193</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.031944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -15598,7 +15598,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUGC.xlsx
+++ b/output/pdf_financials_xlsx/AUGC.xlsx
@@ -8294,7 +8294,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -13207,7 +13211,11 @@
           <t>Income tax recovery 10</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
